--- a/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBA78B0D-A063-4671-9121-DEE9566F9A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE64E856-8B18-47B7-BF78-C9FE2967477A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -717,13 +717,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH04,S01aH03,S03aH02,S04aH05,S04aH08,S02aH04,S02aH05,S04aH02,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S02aH02,S04aH03,S01aH02,S04aH04,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH03</t>
+    <t>S01aH03,S04aH06,S02aH02,S01aH04,S01aH07,S02aH07,S03aH03,S01aH02,S04aH04,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S04aH02,S01aH06,S02aH03,S03aH02,S04aH03,S03aH04,S02aH04,S02aH05,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH09,S04aH09,S04aH02,S03aH08,S03aH10,S01aH10,S03aH02,S03aH09,S01aH09,S03aH01,S02aH01,S02aH10,S04aH08,S01aH08,S02aH08,S01aH01,S04aH01,S01aH02,S02aH02,S04aH10</t>
+    <t>S03aH01,S01aH09,S02aH02,S04aH10,S01aH08,S02aH08,S03aH09,S01aH10,S03aH02,S01aH01,S04aH01,S04aH02,S02aH01,S02aH10,S02aH09,S04aH09,S04aH08,S03aH08,S03aH10,S01aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH09,S04aH09,S04aH02,S03aH08,S03aH10,S01aH10,S03aH02,S03aH09,S01aH09,S03aH01,S02aH01,S02aH10,S04aH08,S01aH08,S02aH08,S01aH01,S04aH01,S01aH02,S02aH02,S04aH10</v>
+        <v>S03aH01,S01aH09,S02aH02,S04aH10,S01aH08,S02aH08,S03aH09,S01aH10,S03aH02,S01aH01,S04aH01,S04aH02,S02aH01,S02aH10,S02aH09,S04aH09,S04aH08,S03aH08,S03aH10,S01aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH04,S01aH03,S03aH02,S04aH05,S04aH08,S02aH04,S02aH05,S04aH02,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S02aH02,S04aH03,S01aH02,S04aH04,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH03</v>
+        <v>S01aH03,S04aH06,S02aH02,S01aH04,S01aH07,S02aH07,S03aH03,S01aH02,S04aH04,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S04aH02,S01aH06,S02aH03,S03aH02,S04aH03,S03aH04,S02aH04,S02aH05,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1446,7 +1446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5477A0-5A4B-4B22-8387-E3E77F6A2983}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AF452F-193D-433F-8FD3-AC410FCBFB6D}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1584,7 +1584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C20326-0E84-4405-B614-395DBCB71B27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9BF46E-7ECB-4BFC-9FF2-39ED59748788}">
   <dimension ref="B9:O1450"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31406,7 +31406,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9C1D13-D300-4766-BA81-9CB9969C81AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F09DFCE-10B6-4ABD-9ED6-9D4D261C8D31}">
   <dimension ref="B9:FT66"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -47437,7 +47437,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E3D442-2E02-4141-B687-4FA2B1730535}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D999FB-710A-4951-BF37-D71AD007DB29}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48027,7 +48027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36262708-3F3B-47E9-A90C-14B67F9CD471}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A96B59-8ADC-4789-866F-4C3B2A691056}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48934,7 +48934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7670C0E0-11AE-45A3-B399-E59BC6DD65BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6484B726-40D8-40D4-B6FF-FF85646BAE47}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49401,7 +49401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3B02B6-E304-405D-8028-2D4B0E8A6D05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D843DD79-73B0-4685-B131-2D936F27BA4D}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49447,7 +49447,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.48293333333333327</v>
+        <v>0.48293333333333338</v>
       </c>
       <c r="E12" t="s">
         <v>233</v>
@@ -49601,7 +49601,7 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>0.68703333333333327</v>
+        <v>0.68703333333333338</v>
       </c>
       <c r="E23" t="s">
         <v>233</v>
@@ -49671,7 +49671,7 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>0.42379999999999995</v>
+        <v>0.42380000000000001</v>
       </c>
       <c r="E28" t="s">
         <v>233</v>
@@ -49839,7 +49839,7 @@
         <v>41</v>
       </c>
       <c r="D40">
-        <v>0.54619999999999991</v>
+        <v>0.54620000000000002</v>
       </c>
       <c r="E40" t="s">
         <v>233</v>
@@ -49937,7 +49937,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.58139999999999992</v>
+        <v>0.58140000000000003</v>
       </c>
       <c r="E47" t="s">
         <v>233</v>
@@ -49965,7 +49965,7 @@
         <v>43</v>
       </c>
       <c r="D49">
-        <v>0.41726666666666662</v>
+        <v>0.41726666666666667</v>
       </c>
       <c r="E49" t="s">
         <v>233</v>
@@ -50091,7 +50091,7 @@
         <v>45</v>
       </c>
       <c r="D58">
-        <v>0.52036666666666676</v>
+        <v>0.52036666666666664</v>
       </c>
       <c r="E58" t="s">
         <v>233</v>
@@ -50119,7 +50119,7 @@
         <v>41</v>
       </c>
       <c r="D60">
-        <v>0.47013333333333335</v>
+        <v>0.47013333333333329</v>
       </c>
       <c r="E60" t="s">
         <v>233</v>
@@ -50161,7 +50161,7 @@
         <v>37</v>
       </c>
       <c r="D63">
-        <v>0.57210000000000005</v>
+        <v>0.57209999999999994</v>
       </c>
       <c r="E63" t="s">
         <v>233</v>
@@ -50217,7 +50217,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.58056666666666668</v>
+        <v>0.58056666666666679</v>
       </c>
       <c r="E67" t="s">
         <v>233</v>
@@ -50231,7 +50231,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.53959999999999997</v>
+        <v>0.53960000000000008</v>
       </c>
       <c r="E68" t="s">
         <v>233</v>
@@ -50245,7 +50245,7 @@
         <v>43</v>
       </c>
       <c r="D69">
-        <v>0.4041333333333334</v>
+        <v>0.40413333333333329</v>
       </c>
       <c r="E69" t="s">
         <v>233</v>
@@ -50273,7 +50273,7 @@
         <v>37</v>
       </c>
       <c r="D71">
-        <v>0.53883333333333328</v>
+        <v>0.53883333333333339</v>
       </c>
       <c r="E71" t="s">
         <v>233</v>
@@ -50315,7 +50315,7 @@
         <v>45</v>
       </c>
       <c r="D74">
-        <v>0.46469999999999995</v>
+        <v>0.46470000000000006</v>
       </c>
       <c r="E74" t="s">
         <v>233</v>
@@ -50427,7 +50427,7 @@
         <v>45</v>
       </c>
       <c r="D82">
-        <v>0.48076666666666673</v>
+        <v>0.48076666666666662</v>
       </c>
       <c r="E82" t="s">
         <v>233</v>
@@ -50441,7 +50441,7 @@
         <v>37</v>
       </c>
       <c r="D83">
-        <v>0.5806</v>
+        <v>0.58059999999999989</v>
       </c>
       <c r="E83" t="s">
         <v>233</v>
@@ -50455,7 +50455,7 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <v>0.44943333333333335</v>
+        <v>0.4494333333333333</v>
       </c>
       <c r="E84" t="s">
         <v>233</v>
@@ -50483,7 +50483,7 @@
         <v>45</v>
       </c>
       <c r="D86">
-        <v>0.48770000000000002</v>
+        <v>0.48769999999999997</v>
       </c>
       <c r="E86" t="s">
         <v>233</v>
@@ -50553,7 +50553,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.46300000000000002</v>
+        <v>0.46299999999999991</v>
       </c>
       <c r="E91" t="s">
         <v>233</v>
@@ -50665,7 +50665,7 @@
         <v>37</v>
       </c>
       <c r="D99">
-        <v>0.5379666666666667</v>
+        <v>0.53796666666666659</v>
       </c>
       <c r="E99" t="s">
         <v>233</v>
@@ -50889,7 +50889,7 @@
         <v>37</v>
       </c>
       <c r="D115">
-        <v>0.55986666666666662</v>
+        <v>0.55986666666666673</v>
       </c>
       <c r="E115" t="s">
         <v>233</v>
@@ -50931,7 +50931,7 @@
         <v>45</v>
       </c>
       <c r="D118">
-        <v>0.49659999999999999</v>
+        <v>0.49659999999999993</v>
       </c>
       <c r="E118" t="s">
         <v>233</v>
@@ -51001,7 +51001,7 @@
         <v>37</v>
       </c>
       <c r="D123">
-        <v>0.57599999999999996</v>
+        <v>0.57600000000000007</v>
       </c>
       <c r="E123" t="s">
         <v>233</v>
@@ -51015,7 +51015,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.42926666666666669</v>
+        <v>0.42926666666666663</v>
       </c>
       <c r="E124" t="s">
         <v>233</v>
@@ -51029,7 +51029,7 @@
         <v>43</v>
       </c>
       <c r="D125">
-        <v>0.42516666666666664</v>
+        <v>0.42516666666666669</v>
       </c>
       <c r="E125" t="s">
         <v>233</v>
